--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486982_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486982_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>M. BECHT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1672</v>
+        <v>2.202</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5238</v>
+        <v>2.7883</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6909</v>
+        <v>-0.5863</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9261</v>
+        <v>2.3741</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0732</v>
+        <v>0.6905</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8529</v>
+        <v>1.6836</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1592</v>
+        <v>2.9698</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8435</v>
+        <v>2.1023</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3157</v>
+        <v>0.8675</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7669</v>
+        <v>-0.5957</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2298</v>
+        <v>-1.4118</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5372</v>
+        <v>0.8161</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.4641</v>
+        <v>1.6427</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7914</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.58</v>
+        <v>-0.3334</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2114</v>
+        <v>-0.3727</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0863</v>
+        <v>-1.1088</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1561</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0698</v>
+        <v>-2.2874</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BECHT</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9666</v>
+        <v>1.5124</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8198</v>
+        <v>0.0673</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8531</v>
+        <v>1.4451</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3741</v>
+        <v>4.5381</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6905</v>
+        <v>0.7758</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6836</v>
+        <v>3.7623</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9698</v>
+        <v>4.9415</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1023</v>
+        <v>1.6006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8675</v>
+        <v>3.3408</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5957</v>
+        <v>-0.4034</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4118</v>
+        <v>-0.8248</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8161</v>
+        <v>0.4215</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6427</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>-5.5442</v>
       </c>
       <c r="R3" t="n">
         <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9414</v>
+        <v>-0.9414</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.302</v>
+        <v>-0.2908</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6395</v>
+        <v>-0.6506</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1088</v>
+        <v>0.7905</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>0.9609</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2874</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8297</v>
+        <v>0.3066</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3782</v>
+        <v>-2.2361</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2079</v>
+        <v>2.5427</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5381</v>
+        <v>2.9261</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7758</v>
+        <v>2.0732</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7623</v>
+        <v>0.8529</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9415</v>
+        <v>2.1592</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6006</v>
+        <v>1.8435</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3408</v>
+        <v>0.3157</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4034</v>
+        <v>0.7669</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8248</v>
+        <v>0.2298</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4215</v>
+        <v>0.5372</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.8748</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.5442</v>
+        <v>-4.1068</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6241</v>
+        <v>0.9308</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.8676</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8877</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7905</v>
+        <v>-1.0863</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9609</v>
+        <v>-1.1561</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1704</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0926</v>
+        <v>0.3016</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.956</v>
+        <v>1.4696</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0487</v>
+        <v>-1.168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1312</v>
+        <v>1.5855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6259</v>
+        <v>-0.0329</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4947</v>
+        <v>1.6185</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.619</v>
+        <v>1.834</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0389</v>
+        <v>-0.1523</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6579</v>
+        <v>1.9863</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7502</v>
+        <v>-0.2485</v>
       </c>
       <c r="N5" t="n">
-        <v>0.587</v>
+        <v>0.1194</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1632</v>
+        <v>-0.3679</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0386</v>
+        <v>-0.4339</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1317</v>
+        <v>-0.3993</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0931</v>
+        <v>-0.0346</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.2874</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.5277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1282</v>
+        <v>0.0601</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1659</v>
+        <v>1.2175</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2941</v>
+        <v>-1.1574</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0129</v>
+        <v>-3.0807</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4336</v>
+        <v>-2.3519</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4208</v>
+        <v>-0.7288</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3326</v>
+        <v>-1.6405</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5695</v>
+        <v>-1.4428</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2368</v>
+        <v>-0.1977</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3198</v>
+        <v>-1.4402</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1358</v>
+        <v>-0.9091</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1839</v>
+        <v>-0.5311</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0109</v>
+        <v>-1.9023</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0386</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0277</v>
+        <v>-1.0458</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1786</v>
+        <v>3.6057</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.1252</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>-0.5195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3639</v>
+        <v>-0.2038</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5669</v>
+        <v>-0.956</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.7522</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5855</v>
+        <v>0.1312</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0329</v>
+        <v>0.6259</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6185</v>
+        <v>-0.4947</v>
       </c>
       <c r="J7" t="n">
-        <v>1.834</v>
+        <v>-0.619</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1523</v>
+        <v>0.0389</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9863</v>
+        <v>-0.6579</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2485</v>
+        <v>0.7502</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1194</v>
+        <v>0.587</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3679</v>
+        <v>0.1632</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0994</v>
+        <v>-0.3351</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.302</v>
+        <v>-0.1317</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2026</v>
+        <v>-0.2033</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2874</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3754</v>
+        <v>-0.2262</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2563</v>
+        <v>1.1272</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6317</v>
+        <v>-1.3534</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0807</v>
+        <v>0.0129</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3519</v>
+        <v>1.4336</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7288</v>
+        <v>-1.4208</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6405</v>
+        <v>1.3326</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4428</v>
+        <v>2.5695</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1977</v>
+        <v>-1.2368</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4402</v>
+        <v>-1.3198</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9091</v>
+        <v>-1.1358</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5311</v>
+        <v>-0.1839</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.3378</v>
+        <v>-0.0871</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8177</v>
+        <v>-0.0001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5201</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>3.6057</v>
+        <v>-1.1786</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5195</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3875</v>
+        <v>-0.3792</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9681</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5806</v>
+        <v>0.3138</v>
       </c>
       <c r="G9" t="n">
         <v>-0.574</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6349</v>
+        <v>-0.6266</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.3836</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0238</v>
+        <v>-0.243</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2416</v>
+        <v>-2.7284</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4867</v>
+        <v>-2.9438</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2451</v>
+        <v>0.2154</v>
       </c>
       <c r="G10" t="n">
         <v>0.3291</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9488</v>
+        <v>0.462</v>
       </c>
       <c r="T10" t="n">
-        <v>0.612</v>
+        <v>0.1548</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3368</v>
+        <v>0.3072</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8768</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9824</v>
+        <v>-3.6093</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9526</v>
+        <v>-2.6387</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0299</v>
+        <v>-0.9706</v>
       </c>
       <c r="G11" t="n">
         <v>1.2445</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0318</v>
+        <v>0.4049</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.124</v>
+        <v>0.1898</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1558</v>
+        <v>0.2151</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7679</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4229</v>
+        <v>-2.764200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4565</v>
+        <v>-2.7977</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03350000000000031</v>
+        <v>0.03350000000000042</v>
       </c>
       <c r="G12" t="n">
         <v>9.486800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6055</v>
+        <v>4.605499999999999</v>
       </c>
       <c r="I12" t="n">
         <v>4.8813</v>
@@ -1366,10 +1366,10 @@
         <v>11.9753</v>
       </c>
       <c r="K12" t="n">
-        <v>8.162700000000001</v>
+        <v>8.162699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>3.8125</v>
+        <v>3.812500000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-2.4885</v>
@@ -1390,10 +1390,10 @@
         <v>14.3738</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.893300000000001</v>
+        <v>-3.2348</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8419</v>
+        <v>-1.1831</v>
       </c>
       <c r="U12" t="n">
         <v>-2.0515</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7682</v>
+        <v>3.2934</v>
       </c>
       <c r="E13" t="n">
-        <v>3.376</v>
+        <v>2.3901</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3922</v>
+        <v>0.9033</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8371</v>
+        <v>0.3414</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4836</v>
+        <v>0.5545</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3208</v>
+        <v>-0.213</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4275</v>
+        <v>2.8475</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7038</v>
+        <v>1.7164</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2763</v>
+        <v>1.1311</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2646</v>
+        <v>-2.5061</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2201</v>
+        <v>-1.1619</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0445</v>
+        <v>-1.3441</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4965</v>
+        <v>0.8862</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7699</v>
+        <v>0.1586</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7266</v>
+        <v>0.7276</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2875</v>
+        <v>0.2177</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6982</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5051</v>
+        <v>2.6326</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0709</v>
+        <v>1.3885</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4341</v>
+        <v>1.244</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1902</v>
+        <v>-0.8371</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1914</v>
+        <v>0.4836</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3816</v>
+        <v>-1.3208</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1373</v>
+        <v>0.4275</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0584</v>
+        <v>1.7038</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0789</v>
+        <v>-1.2763</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0528</v>
+        <v>-1.2646</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2498</v>
+        <v>-1.2201</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3027</v>
+        <v>-0.0445</v>
       </c>
       <c r="P14" t="n">
         <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4935</v>
+        <v>1.3609</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9336</v>
+        <v>0.7824</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5599</v>
+        <v>0.5784</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.2875</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2666</v>
+        <v>1.8338</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5533</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7133</v>
+        <v>1.2859</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3414</v>
+        <v>0.1902</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5545</v>
+        <v>-0.1914</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.213</v>
+        <v>0.3816</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8475</v>
+        <v>0.1373</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7164</v>
+        <v>0.0584</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1311</v>
+        <v>0.0789</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5061</v>
+        <v>0.0528</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1619</v>
+        <v>-0.2498</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3441</v>
+        <v>0.3027</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4641</v>
+        <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1406</v>
+        <v>0.8223</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6782</v>
+        <v>0.4106</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5376</v>
+        <v>0.4117</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2177</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8325</v>
+        <v>1.6223</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0684</v>
+        <v>0.4546</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9009</v>
+        <v>1.1677</v>
       </c>
       <c r="G16" t="n">
         <v>2.7903</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1283</v>
+        <v>0.6615</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2094</v>
+        <v>0.3136</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.3479</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4189</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1553</v>
+        <v>-0.3042</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3173</v>
+        <v>-1.2033</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4726</v>
+        <v>0.8991</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3177</v>
+        <v>-4.6142</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4832</v>
+        <v>-1.7325</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1655</v>
+        <v>-2.8817</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3876</v>
+        <v>-3.9051</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2298</v>
+        <v>-0.9046</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1579</v>
+        <v>-3.0005</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0699</v>
+        <v>-0.709</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.8278</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3234</v>
+        <v>0.1188</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.616</v>
+        <v>2.4641</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4641</v>
+        <v>-0.2053</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4536</v>
+        <v>0.6673</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7592</v>
+        <v>0.3096</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3055</v>
+        <v>0.3576</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2903</v>
+        <v>-0.3079</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6306</v>
+        <v>-0.8984</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3403</v>
+        <v>0.5905</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7988</v>
@@ -1858,13 +1858,13 @@
         <v>3.2855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7673</v>
+        <v>0.7497</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.1282</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6277</v>
+        <v>0.8779</v>
       </c>
       <c r="V18" t="n">
         <v>1.1786</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7397</v>
+        <v>-0.4078</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7306</v>
+        <v>-1.0495</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.4702</v>
+        <v>0.6417</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3933</v>
+        <v>0.3177</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.7274</v>
+        <v>0.4832</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3341</v>
+        <v>-0.1655</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1163</v>
+        <v>1.3876</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2604</v>
+        <v>1.2298</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1441</v>
+        <v>0.1579</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.277</v>
+        <v>-1.0699</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.467</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.3234</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6427</v>
+        <v>-2.4641</v>
       </c>
       <c r="R19" t="n">
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0178</v>
+        <v>-0.1095</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4652</v>
+        <v>0.0269</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5527</v>
+        <v>-0.1364</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4661</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.9548</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1924</v>
+        <v>-0.4478</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2494</v>
+        <v>2.3582</v>
       </c>
       <c r="F20" t="n">
-        <v>0.057</v>
+        <v>-2.806</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6142</v>
+        <v>-3.3933</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7325</v>
+        <v>-3.7274</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8817</v>
+        <v>0.3341</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.9051</v>
+        <v>-1.1163</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9046</v>
+        <v>-2.2604</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.0005</v>
+        <v>1.1441</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.709</v>
+        <v>-2.277</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8278</v>
+        <v>-1.467</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1188</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4641</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.6427</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2209</v>
+        <v>0.2741</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4845</v>
+        <v>0.1116</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>2.4661</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5975</v>
+        <v>4.9548</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4189</v>
+        <v>-2.4886</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8824</v>
+        <v>-3.0968</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4986</v>
+        <v>-4.0216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6162</v>
+        <v>0.9248</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4832</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1901</v>
+        <v>-0.0243</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5384</v>
+        <v>0.0154</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3482</v>
+        <v>-0.0396</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.422900000000001</v>
+        <v>4.817600000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.03350000000000142</v>
+        <v>-0.03350000000000009</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4564</v>
+        <v>4.851</v>
       </c>
       <c r="G22" t="n">
         <v>-9.487</v>
@@ -2140,10 +2140,10 @@
         <v>-4.605599999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.8814</v>
+        <v>-4.881399999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>2.488300000000001</v>
+        <v>2.4883</v>
       </c>
       <c r="K22" t="n">
         <v>3.5574</v>
@@ -2155,7 +2155,7 @@
         <v>-11.9753</v>
       </c>
       <c r="N22" t="n">
-        <v>-8.162600000000001</v>
+        <v>-8.162599999999999</v>
       </c>
       <c r="O22" t="n">
         <v>-3.8125</v>
@@ -2170,19 +2170,19 @@
         <v>18.4808</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8934</v>
+        <v>5.2882</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0515</v>
+        <v>2.0514</v>
       </c>
       <c r="U22" t="n">
-        <v>1.842</v>
+        <v>3.2367</v>
       </c>
       <c r="V22" t="n">
-        <v>4.909600000000001</v>
+        <v>4.909599999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>9.800699999999999</v>
+        <v>9.800700000000001</v>
       </c>
       <c r="X22" t="n">
         <v>-4.891</v>
